--- a/Assets/RawData/Config/攻击参数.xlsx
+++ b/Assets/RawData/Config/攻击参数.xlsx
@@ -7,9 +7,7 @@
     <workbookView windowWidth="24345" windowHeight="12465"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="AtkParm" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -49,9 +47,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
-  <si>
-    <t>##var</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+  <si>
+    <t>##var##mode_list##index_id</t>
   </si>
   <si>
     <t>id</t>
@@ -66,6 +64,12 @@
     <t>radius</t>
   </si>
   <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>posOffset</t>
+  </si>
+  <si>
     <t>atkPhys</t>
   </si>
   <si>
@@ -87,6 +91,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>arrayInt</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -102,16 +109,28 @@
     <t>半径</t>
   </si>
   <si>
+    <t>高度</t>
+  </si>
+  <si>
+    <t>偏移</t>
+  </si>
+  <si>
     <t>攻击力</t>
   </si>
   <si>
-    <t>受击强度等级</t>
+    <t>攻击强度等级</t>
   </si>
   <si>
     <t>命中停顿</t>
   </si>
   <si>
     <t>命中时施加的特殊效果</t>
+  </si>
+  <si>
+    <t>Anbi_Weapon_02</t>
+  </si>
+  <si>
+    <t>[-46,0,0]</t>
   </si>
 </sst>
 </file>
@@ -119,9 +138,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -134,12 +153,50 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -156,14 +213,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,27 +267,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -214,14 +281,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -230,56 +289,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -287,6 +301,11 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -297,6 +316,174 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -309,175 +496,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,6 +507,56 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -515,28 +584,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -555,49 +607,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -606,133 +625,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1085,18 +1104,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
-    <col min="3" max="3" width="12.375" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="6" max="6" width="9.875" customWidth="1"/>
-    <col min="7" max="7" width="12.875" customWidth="1"/>
-    <col min="8" max="8" width="13.125" customWidth="1"/>
-    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="4" max="4" width="18.625" customWidth="1"/>
+    <col min="7" max="7" width="12.75" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="9" width="12.875" customWidth="1"/>
+    <col min="10" max="10" width="13.125" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1124,71 +1145,113 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="2:11">
       <c r="B4">
         <v>1000</v>
       </c>
       <c r="C4">
         <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4">
+        <v>0.06</v>
+      </c>
+      <c r="F4">
+        <v>0.8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1196,26 +1259,4 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
 </file>